--- a/Công việc.xlsx
+++ b/Công việc.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Arduino\Thue\PhanLoaiSanPhamTheoMau_TranTrungChinh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Arduino\Thue\PhanLoaiSanPhamTheoMau_TranTrungChinh\PhanLoaiSanPhamTheoMauCamera\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Cài đặt Python 3.14</t>
   </si>
@@ -53,13 +53,37 @@
   </si>
   <si>
     <t>Nội dung</t>
+  </si>
+  <si>
+    <t>Cài pillow</t>
+  </si>
+  <si>
+    <t>pip install pillow</t>
+  </si>
+  <si>
+    <t>Thử code file test1.py</t>
+  </si>
+  <si>
+    <t>ĐÃ test OK</t>
+  </si>
+  <si>
+    <t>Test2.py</t>
+  </si>
+  <si>
+    <t>Giao diện OK, cần fix lag</t>
+  </si>
+  <si>
+    <t>Test3.py</t>
+  </si>
+  <si>
+    <t>Fig lag do COM, nhưng bị spam data xuốn COM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,8 +99,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -86,6 +117,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -117,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -135,6 +172,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -455,7 +495,7 @@
       <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>3</v>
       </c>
     </row>
@@ -471,24 +511,44 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>

--- a/Công việc.xlsx
+++ b/Công việc.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Cài đặt Python 3.14</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>Fig lag do COM, nhưng bị spam data xuốn COM</t>
+  </si>
+  <si>
+    <t>Test3_fixBG.py vs Arduino</t>
+  </si>
+  <si>
+    <t>Test OK</t>
   </si>
 </sst>
 </file>
@@ -552,8 +558,12 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
